--- a/Data/Mobilitet_i_Telemark/Buss_og_ferge/Punktlighet/RTI_HIST_DETAIL_REGION_LINJE_RAWT_062026.xlsx
+++ b/Data/Mobilitet_i_Telemark/Buss_og_ferge/Punktlighet/RTI_HIST_DETAIL_REGION_LINJE_RAWT_062026.xlsx
@@ -130,18 +130,18 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>910670.0</v>
+        <v>1840378.0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>362769.0</v>
+        <v>700979.0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>547901.0</v>
+        <v>1139399.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>808011.0</v>
+        <v>70001.0</v>
       </c>
       <c r="B4" t="n">
         <v>2026.0</v>
@@ -150,18 +150,18 @@
         <v>6.0</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>5989.0</v>
+        <v>87043.0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2026.0</v>
+        <v>35833.0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3963.0</v>
+        <v>51210.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>808012.0</v>
+        <v>70002.0</v>
       </c>
       <c r="B5" t="n">
         <v>2026.0</v>
@@ -170,18 +170,18 @@
         <v>6.0</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4207.0</v>
+        <v>249402.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>814.0</v>
+        <v>103177.0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3393.0</v>
+        <v>146225.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>808013.0</v>
+        <v>70003.0</v>
       </c>
       <c r="B6" t="n">
         <v>2026.0</v>
@@ -190,18 +190,18 @@
         <v>6.0</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>5159.0</v>
+        <v>20285.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>496.0</v>
+        <v>8584.0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4663.0</v>
+        <v>11701.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>808014.0</v>
+        <v>70004.0</v>
       </c>
       <c r="B7" t="n">
         <v>2026.0</v>
@@ -210,18 +210,18 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>5397.0</v>
+        <v>19327.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1129.0</v>
+        <v>9179.0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4268.0</v>
+        <v>10148.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>808015.0</v>
+        <v>70011.0</v>
       </c>
       <c r="B8" t="n">
         <v>2026.0</v>
@@ -230,18 +230,18 @@
         <v>6.0</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>958.0</v>
+        <v>489.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>319.0</v>
+        <v>128.0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>639.0</v>
+        <v>361.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>808016.0</v>
+        <v>70021.0</v>
       </c>
       <c r="B9" t="n">
         <v>2026.0</v>
@@ -250,18 +250,18 @@
         <v>6.0</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1733.0</v>
+        <v>157.0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>252.0</v>
+        <v>69.0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1481.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>808041.0</v>
+        <v>70022.0</v>
       </c>
       <c r="B10" t="n">
         <v>2026.0</v>
@@ -270,18 +270,18 @@
         <v>6.0</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>225537.0</v>
+        <v>14987.0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>102681.0</v>
+        <v>5513.0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>122856.0</v>
+        <v>9474.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>808042.0</v>
+        <v>70023.0</v>
       </c>
       <c r="B11" t="n">
         <v>2026.0</v>
@@ -290,18 +290,18 @@
         <v>6.0</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>97753.0</v>
+        <v>327.0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>47410.0</v>
+        <v>190.0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>50343.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>808043.0</v>
+        <v>70042.0</v>
       </c>
       <c r="B12" t="n">
         <v>2026.0</v>
@@ -310,18 +310,18 @@
         <v>6.0</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>111243.0</v>
+        <v>1973.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>44554.0</v>
+        <v>701.0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>66689.0</v>
+        <v>1272.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>808044.0</v>
+        <v>70043.0</v>
       </c>
       <c r="B13" t="n">
         <v>2026.0</v>
@@ -330,18 +330,18 @@
         <v>6.0</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>10312.0</v>
+        <v>1463.0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3849.0</v>
+        <v>411.0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>6463.0</v>
+        <v>1052.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>808045.0</v>
+        <v>70045.0</v>
       </c>
       <c r="B14" t="n">
         <v>2026.0</v>
@@ -350,18 +350,18 @@
         <v>6.0</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>33461.0</v>
+        <v>15188.0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16312.0</v>
+        <v>3390.0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>17149.0</v>
+        <v>11798.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>808046.0</v>
+        <v>70046.0</v>
       </c>
       <c r="B15" t="n">
         <v>2026.0</v>
@@ -370,18 +370,18 @@
         <v>6.0</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>28373.0</v>
+        <v>11061.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7325.0</v>
+        <v>2479.0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>21048.0</v>
+        <v>8582.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>808047.0</v>
+        <v>70070.0</v>
       </c>
       <c r="B16" t="n">
         <v>2026.0</v>
@@ -390,18 +390,18 @@
         <v>6.0</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>43065.0</v>
+        <v>6110.0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13153.0</v>
+        <v>2206.0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>29912.0</v>
+        <v>3904.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>808048.0</v>
+        <v>70071.0</v>
       </c>
       <c r="B17" t="n">
         <v>2026.0</v>
@@ -410,18 +410,18 @@
         <v>6.0</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>28988.0</v>
+        <v>3643.0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11638.0</v>
+        <v>1077.0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17350.0</v>
+        <v>2566.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>808049.0</v>
+        <v>70093.0</v>
       </c>
       <c r="B18" t="n">
         <v>2026.0</v>
@@ -430,18 +430,18 @@
         <v>6.0</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>13096.0</v>
+        <v>5473.0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>3446.0</v>
+        <v>1441.0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9650.0</v>
+        <v>4032.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>808050.0</v>
+        <v>70094.0</v>
       </c>
       <c r="B19" t="n">
         <v>2026.0</v>
@@ -450,18 +450,18 @@
         <v>6.0</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>16584.0</v>
+        <v>391.0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6944.0</v>
+        <v>120.0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9640.0</v>
+        <v>271.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>808080.0</v>
+        <v>70095.0</v>
       </c>
       <c r="B20" t="n">
         <v>2026.0</v>
@@ -470,18 +470,18 @@
         <v>6.0</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>3811.0</v>
+        <v>2724.0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>706.0</v>
+        <v>699.0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3105.0</v>
+        <v>2025.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>808084.0</v>
+        <v>70096.0</v>
       </c>
       <c r="B21" t="n">
         <v>2026.0</v>
@@ -490,18 +490,18 @@
         <v>6.0</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>3410.0</v>
+        <v>31073.0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>738.0</v>
+        <v>10727.0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2672.0</v>
+        <v>20346.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>808101.0</v>
+        <v>70100.0</v>
       </c>
       <c r="B22" t="n">
         <v>2026.0</v>
@@ -510,18 +510,18 @@
         <v>6.0</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>345.0</v>
+        <v>265.0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>100.0</v>
+        <v>71.0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>245.0</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>808102.0</v>
+        <v>70108.0</v>
       </c>
       <c r="B23" t="n">
         <v>2026.0</v>
@@ -530,18 +530,18 @@
         <v>6.0</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>7535.0</v>
+        <v>47763.0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3670.0</v>
+        <v>16792.0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3865.0</v>
+        <v>30971.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>808103.0</v>
+        <v>70109.0</v>
       </c>
       <c r="B24" t="n">
         <v>2026.0</v>
@@ -550,18 +550,18 @@
         <v>6.0</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>7669.0</v>
+        <v>52469.0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4328.0</v>
+        <v>8694.0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3341.0</v>
+        <v>43775.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>808104.0</v>
+        <v>70110.0</v>
       </c>
       <c r="B25" t="n">
         <v>2026.0</v>
@@ -570,18 +570,18 @@
         <v>6.0</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>385.0</v>
+        <v>341.0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>51.0</v>
+        <v>79.0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>334.0</v>
+        <v>262.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>808111.0</v>
+        <v>70111.0</v>
       </c>
       <c r="B26" t="n">
         <v>2026.0</v>
@@ -590,18 +590,18 @@
         <v>6.0</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>1111.0</v>
+        <v>18823.0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>527.0</v>
+        <v>6007.0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>584.0</v>
+        <v>12816.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>808113.0</v>
+        <v>70112.0</v>
       </c>
       <c r="B27" t="n">
         <v>2026.0</v>
@@ -610,18 +610,18 @@
         <v>6.0</v>
       </c>
       <c r="D27" s="1" t="n">
+        <v>408.0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>386.0</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>22.0</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>20.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>808115.0</v>
+        <v>70113.0</v>
       </c>
       <c r="B28" t="n">
         <v>2026.0</v>
@@ -630,18 +630,18 @@
         <v>6.0</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>445.0</v>
+        <v>89894.0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>220.0</v>
+        <v>27005.0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>225.0</v>
+        <v>62889.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>808116.0</v>
+        <v>70115.0</v>
       </c>
       <c r="B29" t="n">
         <v>2026.0</v>
@@ -650,18 +650,18 @@
         <v>6.0</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>6084.0</v>
+        <v>17374.0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1866.0</v>
+        <v>4758.0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4218.0</v>
+        <v>12616.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>808117.0</v>
+        <v>70116.0</v>
       </c>
       <c r="B30" t="n">
         <v>2026.0</v>
@@ -670,18 +670,18 @@
         <v>6.0</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>208.0</v>
+        <v>61956.0</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>49.0</v>
+        <v>23961.0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>159.0</v>
+        <v>37995.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>808121.0</v>
+        <v>70117.0</v>
       </c>
       <c r="B31" t="n">
         <v>2026.0</v>
@@ -690,18 +690,18 @@
         <v>6.0</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>577.0</v>
+        <v>834.0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>90.0</v>
+        <v>406.0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>487.0</v>
+        <v>428.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>808122.0</v>
+        <v>70118.0</v>
       </c>
       <c r="B32" t="n">
         <v>2026.0</v>
@@ -710,18 +710,18 @@
         <v>6.0</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>468.0</v>
+        <v>226.0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.0</v>
+        <v>63.0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>386.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>808123.0</v>
+        <v>70120.0</v>
       </c>
       <c r="B33" t="n">
         <v>2026.0</v>
@@ -730,18 +730,18 @@
         <v>6.0</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>1065.0</v>
+        <v>223.0</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>142.0</v>
+        <v>99.0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>923.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>808127.0</v>
+        <v>70126.0</v>
       </c>
       <c r="B34" t="n">
         <v>2026.0</v>
@@ -750,18 +750,18 @@
         <v>6.0</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>1333.0</v>
+        <v>26.0</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>329.0</v>
+        <v>25.0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1004.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>808128.0</v>
+        <v>70130.0</v>
       </c>
       <c r="B35" t="n">
         <v>2026.0</v>
@@ -770,18 +770,18 @@
         <v>6.0</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>346.0</v>
+        <v>47384.0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>64.0</v>
+        <v>20469.0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>282.0</v>
+        <v>26915.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>808129.0</v>
+        <v>70134.0</v>
       </c>
       <c r="B36" t="n">
         <v>2026.0</v>
@@ -790,18 +790,18 @@
         <v>6.0</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>575.0</v>
+        <v>39.0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>487.0</v>
+        <v>8.0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>88.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>808131.0</v>
+        <v>70138.0</v>
       </c>
       <c r="B37" t="n">
         <v>2026.0</v>
@@ -810,18 +810,18 @@
         <v>6.0</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>4019.0</v>
+        <v>218.0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1718.0</v>
+        <v>132.0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2301.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>808132.0</v>
+        <v>70150.0</v>
       </c>
       <c r="B38" t="n">
         <v>2026.0</v>
@@ -830,18 +830,18 @@
         <v>6.0</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>1526.0</v>
+        <v>1790.0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>459.0</v>
+        <v>411.0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1067.0</v>
+        <v>1379.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>808133.0</v>
+        <v>70161.0</v>
       </c>
       <c r="B39" t="n">
         <v>2026.0</v>
@@ -850,18 +850,18 @@
         <v>6.0</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>613.0</v>
+        <v>6388.0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>128.0</v>
+        <v>3545.0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>485.0</v>
+        <v>2843.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>808135.0</v>
+        <v>70163.0</v>
       </c>
       <c r="B40" t="n">
         <v>2026.0</v>
@@ -870,18 +870,18 @@
         <v>6.0</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>349.0</v>
+        <v>187.0</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>134.0</v>
+        <v>22.0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>215.0</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>808136.0</v>
+        <v>70168.0</v>
       </c>
       <c r="B41" t="n">
         <v>2026.0</v>
@@ -890,18 +890,18 @@
         <v>6.0</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>431.0</v>
+        <v>116.0</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>86.0</v>
+        <v>7.0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>345.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>808140.0</v>
+        <v>70172.0</v>
       </c>
       <c r="B42" t="n">
         <v>2026.0</v>
@@ -910,18 +910,18 @@
         <v>6.0</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>1058.0</v>
+        <v>5239.0</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>623.0</v>
+        <v>916.0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>435.0</v>
+        <v>4323.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>808141.0</v>
+        <v>70176.0</v>
       </c>
       <c r="B43" t="n">
         <v>2026.0</v>
@@ -930,18 +930,18 @@
         <v>6.0</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>1073.0</v>
+        <v>547.0</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>155.0</v>
+        <v>111.0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>918.0</v>
+        <v>436.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>808142.0</v>
+        <v>70206.0</v>
       </c>
       <c r="B44" t="n">
         <v>2026.0</v>
@@ -950,18 +950,18 @@
         <v>6.0</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>1536.0</v>
+        <v>79.0</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>301.0</v>
+        <v>11.0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1235.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>808143.0</v>
+        <v>70208.0</v>
       </c>
       <c r="B45" t="n">
         <v>2026.0</v>
@@ -970,18 +970,18 @@
         <v>6.0</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>4190.0</v>
+        <v>10138.0</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1530.0</v>
+        <v>4061.0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>2660.0</v>
+        <v>6077.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>808144.0</v>
+        <v>70210.0</v>
       </c>
       <c r="B46" t="n">
         <v>2026.0</v>
@@ -990,18 +990,18 @@
         <v>6.0</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>556.0</v>
+        <v>11324.0</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>117.0</v>
+        <v>4406.0</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>439.0</v>
+        <v>6918.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>808145.0</v>
+        <v>701112.0</v>
       </c>
       <c r="B47" t="n">
         <v>2026.0</v>
@@ -1010,18 +1010,20 @@
         <v>6.0</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>248.0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>247.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>808146.0</v>
+        <v>701120.0</v>
       </c>
       <c r="B48" t="n">
         <v>2026.0</v>
@@ -1030,18 +1032,18 @@
         <v>6.0</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>220.0</v>
+        <v>28.0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>201.0</v>
+        <v>16.0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>808147.0</v>
+        <v>701121.0</v>
       </c>
       <c r="B49" t="n">
         <v>2026.0</v>
@@ -1050,18 +1052,18 @@
         <v>6.0</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>42.0</v>
+        <v>251.0</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.0</v>
+        <v>96.0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>28.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>808150.0</v>
+        <v>701126.0</v>
       </c>
       <c r="B50" t="n">
         <v>2026.0</v>
@@ -1070,18 +1072,18 @@
         <v>6.0</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>194.0</v>
+        <v>58.0</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.0</v>
+        <v>28.0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>90.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>808151.0</v>
+        <v>701134.0</v>
       </c>
       <c r="B51" t="n">
         <v>2026.0</v>
@@ -1090,18 +1092,20 @@
         <v>6.0</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>1057.0</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>373.0</v>
+        <v>9.0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>684.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>808182.0</v>
+        <v>701135.0</v>
       </c>
       <c r="B52" t="n">
         <v>2026.0</v>
@@ -1110,18 +1114,18 @@
         <v>6.0</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>48688.0</v>
+        <v>75.0</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>21578.0</v>
+        <v>30.0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>27110.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>808185.0</v>
+        <v>701144.0</v>
       </c>
       <c r="B53" t="n">
         <v>2026.0</v>
@@ -1130,18 +1134,20 @@
         <v>6.0</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>22355.0</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>10068.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12287.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>808209.0</v>
+        <v>701148.0</v>
       </c>
       <c r="B54" t="n">
         <v>2026.0</v>
@@ -1150,18 +1156,18 @@
         <v>6.0</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>13343.0</v>
+        <v>39.0</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>5522.0</v>
+        <v>10.0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>7821.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>808210.0</v>
+        <v>701200.0</v>
       </c>
       <c r="B55" t="n">
         <v>2026.0</v>
@@ -1170,18 +1176,18 @@
         <v>6.0</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>827.0</v>
+        <v>9.0</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>156.0</v>
+        <v>8.0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>671.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>808301.0</v>
+        <v>701212.0</v>
       </c>
       <c r="B56" t="n">
         <v>2026.0</v>
@@ -1190,18 +1196,18 @@
         <v>6.0</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>9531.0</v>
+        <v>17.0</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2442.0</v>
+        <v>2.0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>7089.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>808305.0</v>
+        <v>701223.0</v>
       </c>
       <c r="B57" t="n">
         <v>2026.0</v>
@@ -1210,18 +1216,18 @@
         <v>6.0</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>4038.0</v>
+        <v>68.0</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>1077.0</v>
+        <v>17.0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>2961.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>808312.0</v>
+        <v>701236.0</v>
       </c>
       <c r="B58" t="n">
         <v>2026.0</v>
@@ -1230,18 +1236,20 @@
         <v>6.0</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>1213.0</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>205.0</v>
+        <v>21.0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1008.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>808313.0</v>
+        <v>701237.0</v>
       </c>
       <c r="B59" t="n">
         <v>2026.0</v>
@@ -1250,18 +1258,20 @@
         <v>6.0</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>322.0</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>43.0</v>
+        <v>41.0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>279.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>808320.0</v>
+        <v>701238.0</v>
       </c>
       <c r="B60" t="n">
         <v>2026.0</v>
@@ -1270,18 +1280,18 @@
         <v>6.0</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>166.0</v>
+        <v>121.0</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>30.0</v>
+        <v>49.0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>136.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>808321.0</v>
+        <v>701242.0</v>
       </c>
       <c r="B61" t="n">
         <v>2026.0</v>
@@ -1290,18 +1300,18 @@
         <v>6.0</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>336.0</v>
+        <v>29.0</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.0</v>
+        <v>6.0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>233.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>808322.0</v>
+        <v>701243.0</v>
       </c>
       <c r="B62" t="n">
         <v>2026.0</v>
@@ -1310,18 +1320,20 @@
         <v>6.0</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>2123.0</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>636.0</v>
+        <v>10.0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1487.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>808323.0</v>
+        <v>701263.0</v>
       </c>
       <c r="B63" t="n">
         <v>2026.0</v>
@@ -1330,18 +1342,20 @@
         <v>6.0</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>16223.0</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>3711.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>12512.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>808324.0</v>
+        <v>701264.0</v>
       </c>
       <c r="B64" t="n">
         <v>2026.0</v>
@@ -1350,18 +1364,20 @@
         <v>6.0</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>3777.0</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>1375.0</v>
+        <v>22.0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2402.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>808325.0</v>
+        <v>701266.0</v>
       </c>
       <c r="B65" t="n">
         <v>2026.0</v>
@@ -1370,18 +1386,20 @@
         <v>6.0</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>3947.0</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>1082.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2865.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>808459.0</v>
+        <v>701272.0</v>
       </c>
       <c r="B66" t="n">
         <v>2026.0</v>
@@ -1390,18 +1408,18 @@
         <v>6.0</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>16289.0</v>
+        <v>7.0</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>7922.0</v>
+        <v>1.0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>8367.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>808460.0</v>
+        <v>701273.0</v>
       </c>
       <c r="B67" t="n">
         <v>2026.0</v>
@@ -1410,18 +1428,20 @@
         <v>6.0</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>341.0</v>
+        <v>9.0</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>252.0</v>
+        <v>9.0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>808461.0</v>
+        <v>701274.0</v>
       </c>
       <c r="B68" t="n">
         <v>2026.0</v>
@@ -1430,18 +1450,20 @@
         <v>6.0</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>1626.0</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>611.0</v>
+        <v>8.0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1015.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>808462.0</v>
+        <v>701281.0</v>
       </c>
       <c r="B69" t="n">
         <v>2026.0</v>
@@ -1450,18 +1472,18 @@
         <v>6.0</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>338.0</v>
+        <v>68.0</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>59.0</v>
+        <v>11.0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>279.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>808463.0</v>
+        <v>701284.0</v>
       </c>
       <c r="B70" t="n">
         <v>2026.0</v>
@@ -1470,18 +1492,20 @@
         <v>6.0</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>430.0</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>110.0</v>
+        <v>23.0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>320.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>808501.0</v>
+        <v>701313.0</v>
       </c>
       <c r="B71" t="n">
         <v>2026.0</v>
@@ -1490,18 +1514,18 @@
         <v>6.0</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>2589.0</v>
+        <v>6.0</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>617.0</v>
+        <v>5.0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1972.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>808502.0</v>
+        <v>701314.0</v>
       </c>
       <c r="B72" t="n">
         <v>2026.0</v>
@@ -1510,18 +1534,18 @@
         <v>6.0</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>1135.0</v>
+        <v>10.0</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>358.0</v>
+        <v>4.0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>777.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>808504.0</v>
+        <v>701315.0</v>
       </c>
       <c r="B73" t="n">
         <v>2026.0</v>
@@ -1530,18 +1554,20 @@
         <v>6.0</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>128.0</v>
-      </c>
-      <c r="E73" s="2" t="n">
-        <v>12.0</v>
+        <v>38.0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>116.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>808506.0</v>
+        <v>701450.0</v>
       </c>
       <c r="B74" t="n">
         <v>2026.0</v>
@@ -1550,18 +1576,20 @@
         <v>6.0</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>11597.0</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>2608.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>8989.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>808507.0</v>
+        <v>701451.0</v>
       </c>
       <c r="B75" t="n">
         <v>2026.0</v>
@@ -1570,18 +1598,20 @@
         <v>6.0</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>287.0</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>26.0</v>
+        <v>15.0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>261.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>808508.0</v>
+        <v>701456.0</v>
       </c>
       <c r="B76" t="n">
         <v>2026.0</v>
@@ -1590,20 +1620,20 @@
         <v>6.0</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="E76" t="inlineStr">
+        <v>10.0</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t/>
         </is>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>76.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>808601.0</v>
+        <v>701457.0</v>
       </c>
       <c r="B77" t="n">
         <v>2026.0</v>
@@ -1612,18 +1642,18 @@
         <v>6.0</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>7329.0</v>
+        <v>4.0</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4135.0</v>
+        <v>2.0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>3194.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>808602.0</v>
+        <v>701460.0</v>
       </c>
       <c r="B78" t="n">
         <v>2026.0</v>
@@ -1632,18 +1662,20 @@
         <v>6.0</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>1048.0</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>319.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>729.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>808603.0</v>
+        <v>701472.0</v>
       </c>
       <c r="B79" t="n">
         <v>2026.0</v>
@@ -1652,18 +1684,20 @@
         <v>6.0</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>2709.0</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>1018.0</v>
+        <v>21.0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1691.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>808605.0</v>
+        <v>701476.0</v>
       </c>
       <c r="B80" t="n">
         <v>2026.0</v>
@@ -1672,18 +1706,18 @@
         <v>6.0</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>124.0</v>
+        <v>11.0</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>30.0</v>
+        <v>1.0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>94.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>808606.0</v>
+        <v>701478.0</v>
       </c>
       <c r="B81" t="n">
         <v>2026.0</v>
@@ -1692,18 +1726,18 @@
         <v>6.0</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>675.0</v>
+        <v>25.0</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>158.0</v>
+        <v>12.0</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>517.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>808607.0</v>
+        <v>701486.0</v>
       </c>
       <c r="B82" t="n">
         <v>2026.0</v>
@@ -1712,18 +1746,20 @@
         <v>6.0</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>10191.0</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>3584.0</v>
+        <v>21.0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>6607.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>808609.0</v>
+        <v>701487.0</v>
       </c>
       <c r="B83" t="n">
         <v>2026.0</v>
@@ -1732,18 +1768,18 @@
         <v>6.0</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>13418.0</v>
+        <v>97.0</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>3277.0</v>
+        <v>60.0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>10141.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>808610.0</v>
+        <v>701489.0</v>
       </c>
       <c r="B84" t="n">
         <v>2026.0</v>
@@ -1752,18 +1788,20 @@
         <v>6.0</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>220.0</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>31.0</v>
+        <v>15.0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>189.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>808701.0</v>
+        <v>701495.0</v>
       </c>
       <c r="B85" t="n">
         <v>2026.0</v>
@@ -1772,18 +1810,18 @@
         <v>6.0</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>3166.0</v>
+        <v>8.0</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1072.0</v>
+        <v>2.0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2094.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>808702.0</v>
+        <v>701506.0</v>
       </c>
       <c r="B86" t="n">
         <v>2026.0</v>
@@ -1792,18 +1830,18 @@
         <v>6.0</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>291.0</v>
+        <v>60.0</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>129.0</v>
+        <v>40.0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>162.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>808801.0</v>
+        <v>701508.0</v>
       </c>
       <c r="B87" t="n">
         <v>2026.0</v>
@@ -1812,18 +1850,18 @@
         <v>6.0</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>447.0</v>
+        <v>261.0</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>62.0</v>
+        <v>41.0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>385.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>808802.0</v>
+        <v>701509.0</v>
       </c>
       <c r="B88" t="n">
         <v>2026.0</v>
@@ -1832,18 +1870,18 @@
         <v>6.0</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>199.0</v>
+        <v>73.0</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>159.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>808803.0</v>
+        <v>701510.0</v>
       </c>
       <c r="B89" t="n">
         <v>2026.0</v>
@@ -1852,18 +1890,18 @@
         <v>6.0</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>927.0</v>
+        <v>90.0</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>108.0</v>
+        <v>31.0</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>819.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>808804.0</v>
+        <v>701519.0</v>
       </c>
       <c r="B90" t="n">
         <v>2026.0</v>
@@ -1872,18 +1910,18 @@
         <v>6.0</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>396.0</v>
+        <v>70.0</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>28.0</v>
+        <v>48.0</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>368.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>808805.0</v>
+        <v>701530.0</v>
       </c>
       <c r="B91" t="n">
         <v>2026.0</v>
@@ -1892,18 +1930,18 @@
         <v>6.0</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>573.0</v>
+        <v>47.0</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>229.0</v>
+        <v>5.0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>344.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>808807.0</v>
+        <v>701531.0</v>
       </c>
       <c r="B92" t="n">
         <v>2026.0</v>
@@ -1912,18 +1950,18 @@
         <v>6.0</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>531.0</v>
+        <v>102.0</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>62.0</v>
+        <v>8.0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>469.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>808808.0</v>
+        <v>701533.0</v>
       </c>
       <c r="B93" t="n">
         <v>2026.0</v>
@@ -1932,18 +1970,18 @@
         <v>6.0</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>503.0</v>
+        <v>170.0</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>145.0</v>
+        <v>76.0</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>358.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>808809.0</v>
+        <v>701536.0</v>
       </c>
       <c r="B94" t="n">
         <v>2026.0</v>
@@ -1952,18 +1990,18 @@
         <v>6.0</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>331.0</v>
+        <v>13.0</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>133.0</v>
+        <v>4.0</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>198.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>808810.0</v>
+        <v>701537.0</v>
       </c>
       <c r="B95" t="n">
         <v>2026.0</v>
@@ -1972,20 +2010,18 @@
         <v>6.0</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>45.0</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>3.0</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>12.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>808811.0</v>
+        <v>701538.0</v>
       </c>
       <c r="B96" t="n">
         <v>2026.0</v>
@@ -1994,18 +2030,18 @@
         <v>6.0</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>354.0</v>
+        <v>33.0</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>81.0</v>
+        <v>1.0</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>273.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>808812.0</v>
+        <v>701539.0</v>
       </c>
       <c r="B97" t="n">
         <v>2026.0</v>
@@ -2014,18 +2050,18 @@
         <v>6.0</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>69.0</v>
+        <v>75.0</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>21.0</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>808814.0</v>
+        <v>701541.0</v>
       </c>
       <c r="B98" t="n">
         <v>2026.0</v>
@@ -2034,18 +2070,18 @@
         <v>6.0</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>759.0</v>
+        <v>20.0</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>172.0</v>
+        <v>6.0</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>587.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>808816.0</v>
+        <v>701542.0</v>
       </c>
       <c r="B99" t="n">
         <v>2026.0</v>
@@ -2054,18 +2090,20 @@
         <v>6.0</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>144.0</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>18.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>126.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>808817.0</v>
+        <v>701543.0</v>
       </c>
       <c r="B100" t="n">
         <v>2026.0</v>
@@ -2074,18 +2112,18 @@
         <v>6.0</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>336.0</v>
+        <v>127.0</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>22.0</v>
+        <v>14.0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>314.0</v>
+        <v>113.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>808818.0</v>
+        <v>701544.0</v>
       </c>
       <c r="B101" t="n">
         <v>2026.0</v>
@@ -2094,18 +2132,20 @@
         <v>6.0</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>354.0</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>31.0</v>
+        <v>23.0</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>323.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>808819.0</v>
+        <v>701545.0</v>
       </c>
       <c r="B102" t="n">
         <v>2026.0</v>
@@ -2114,18 +2154,20 @@
         <v>6.0</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>620.0</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>155.0</v>
+        <v>26.0</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>465.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>808822.0</v>
+        <v>701548.0</v>
       </c>
       <c r="B103" t="n">
         <v>2026.0</v>
@@ -2134,18 +2176,18 @@
         <v>6.0</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>114.0</v>
+        <v>165.0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>141.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>808877.0</v>
+        <v>701550.0</v>
       </c>
       <c r="B104" t="n">
         <v>2026.0</v>
@@ -2154,18 +2196,18 @@
         <v>6.0</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>926.0</v>
+        <v>113.0</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>244.0</v>
+        <v>18.0</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>682.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>808881.0</v>
+        <v>701551.0</v>
       </c>
       <c r="B105" t="n">
         <v>2026.0</v>
@@ -2174,18 +2216,18 @@
         <v>6.0</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>4988.0</v>
+        <v>379.0</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>1911.0</v>
+        <v>75.0</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>3077.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>808882.0</v>
+        <v>701552.0</v>
       </c>
       <c r="B106" t="n">
         <v>2026.0</v>
@@ -2194,18 +2236,20 @@
         <v>6.0</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>3693.0</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>700.0</v>
+        <v>64.0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>2993.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>808885.0</v>
+        <v>701553.0</v>
       </c>
       <c r="B107" t="n">
         <v>2026.0</v>
@@ -2214,18 +2258,20 @@
         <v>6.0</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>387.0</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>70.0</v>
+        <v>26.0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>317.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>808887.0</v>
+        <v>701554.0</v>
       </c>
       <c r="B108" t="n">
         <v>2026.0</v>
@@ -2234,18 +2280,18 @@
         <v>6.0</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>960.0</v>
+        <v>88.0</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>146.0</v>
+        <v>8.0</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>814.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>808888.0</v>
+        <v>701555.0</v>
       </c>
       <c r="B109" t="n">
         <v>2026.0</v>
@@ -2254,18 +2300,18 @@
         <v>6.0</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>677.0</v>
+        <v>47.0</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>674.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>808892.0</v>
+        <v>701557.0</v>
       </c>
       <c r="B110" t="n">
         <v>2026.0</v>
@@ -2274,18 +2320,20 @@
         <v>6.0</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>754.0</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>171.0</v>
+        <v>49.0</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>583.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>808894.0</v>
+        <v>701560.0</v>
       </c>
       <c r="B111" t="n">
         <v>2026.0</v>
@@ -2294,18 +2342,18 @@
         <v>6.0</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>659.0</v>
+        <v>142.0</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>111.0</v>
+        <v>70.0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>548.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>808896.0</v>
+        <v>701561.0</v>
       </c>
       <c r="B112" t="n">
         <v>2026.0</v>
@@ -2314,18 +2362,20 @@
         <v>6.0</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>668.0</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>203.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>465.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>808898.0</v>
+        <v>701562.0</v>
       </c>
       <c r="B113" t="n">
         <v>2026.0</v>
@@ -2334,18 +2384,20 @@
         <v>6.0</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>141.0</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>36.0</v>
+        <v>25.0</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>105.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>808899.0</v>
+        <v>701566.0</v>
       </c>
       <c r="B114" t="n">
         <v>2026.0</v>
@@ -2354,18 +2406,18 @@
         <v>6.0</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>509.0</v>
+        <v>126.0</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>187.0</v>
+        <v>32.0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>322.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>808901.0</v>
+        <v>701567.0</v>
       </c>
       <c r="B115" t="n">
         <v>2026.0</v>
@@ -2374,18 +2426,18 @@
         <v>6.0</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>2505.0</v>
+        <v>143.0</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>1189.0</v>
+        <v>72.0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1316.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>808902.0</v>
+        <v>701571.0</v>
       </c>
       <c r="B116" t="n">
         <v>2026.0</v>
@@ -2394,33 +2446,3889 @@
         <v>6.0</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>1065.0</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>296.0</v>
+        <v>20.0</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>769.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
+        <v>701572.0</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C117" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>730.0</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>572.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>701573.0</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>59.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>701575.0</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>197.0</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>101.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>701576.0</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>76.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>701577.0</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>375.0</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>372.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>701579.0</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C122" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>701580.0</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>701582.0</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C124" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>701583.0</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>701585.0</v>
+      </c>
+      <c r="B126" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>701591.0</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>52.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>701592.0</v>
+      </c>
+      <c r="B128" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>701593.0</v>
+      </c>
+      <c r="B129" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>33.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>701596.0</v>
+      </c>
+      <c r="B130" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>76.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>701601.0</v>
+      </c>
+      <c r="B131" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C131" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>98.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>701605.0</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C132" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>193.0</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>149.0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>701609.0</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>296.0</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>254.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>701610.0</v>
+      </c>
+      <c r="B134" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>701620.0</v>
+      </c>
+      <c r="B135" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C135" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>58.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>701623.0</v>
+      </c>
+      <c r="B136" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>128.0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>701626.0</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C137" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>79.0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>701631.0</v>
+      </c>
+      <c r="B138" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>161.0</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>136.0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>701635.0</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>227.0</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>199.0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>701640.0</v>
+      </c>
+      <c r="B140" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>607.0</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>528.0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>701641.0</v>
+      </c>
+      <c r="B141" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>701657.0</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>701670.0</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C143" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>701671.0</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C144" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>83.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>701674.0</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C145" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>701685.0</v>
+      </c>
+      <c r="B146" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C146" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>701688.0</v>
+      </c>
+      <c r="B147" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C147" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>701690.0</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C148" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>701696.0</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C149" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>701697.0</v>
+      </c>
+      <c r="B150" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C150" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>701698.0</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C151" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>701699.0</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C152" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>130.0</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>108.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>701701.0</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C153" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>103.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>701709.0</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C154" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>701712.0</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C155" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>701713.0</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C156" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>701733.0</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C157" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>701736.0</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C158" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>43.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>701800.0</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C159" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>29.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>701801.0</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C160" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>701803.0</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C161" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>57.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>701811.0</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C162" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>34.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>701812.0</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C163" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>701813.0</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C164" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>56.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>701814.0</v>
+      </c>
+      <c r="B165" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C165" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>701816.0</v>
+      </c>
+      <c r="B166" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C166" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>701817.0</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C167" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>345.0</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>251.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>701818.0</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C168" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>701820.0</v>
+      </c>
+      <c r="B169" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C169" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>191.0</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>182.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>701821.0</v>
+      </c>
+      <c r="B170" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C170" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>701823.0</v>
+      </c>
+      <c r="B171" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C171" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>701826.0</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C172" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>701828.0</v>
+      </c>
+      <c r="B173" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C173" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>701829.0</v>
+      </c>
+      <c r="B174" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C174" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>701830.0</v>
+      </c>
+      <c r="B175" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C175" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>41.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>701831.0</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C176" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D176" s="1" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>51.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>701832.0</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C177" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D177" s="1" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>701900.0</v>
+      </c>
+      <c r="B178" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C178" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D178" s="1" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>701901.0</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C179" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D179" s="1" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>701903.0</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C180" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>701906.0</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C181" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>110.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>701907.0</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C182" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>42.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>701908.0</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>701912.0</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C184" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>67.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>701919.0</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>224.0</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>701920.0</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C186" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>701924.0</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C187" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>79.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>701927.0</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>705002.0</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C189" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>722.0</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>264.0</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>458.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>705113.0</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>705116.0</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>124.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>705130.0</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C192" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>298.0</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>298.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>808011.0</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C193" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>6454.0</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>2235.0</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>4219.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>808012.0</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C194" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>4613.0</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>922.0</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>3691.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>808013.0</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C195" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>5661.0</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>559.0</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>5102.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>808014.0</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>5837.0</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>1267.0</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>4570.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>808015.0</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C197" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>1027.0</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>336.0</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>691.0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>808016.0</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>1840.0</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>253.0</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>1587.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>808041.0</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>244225.0</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>111138.0</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>133087.0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>808042.0</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C200" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>105974.0</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>50330.0</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>55644.0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>808043.0</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>120586.0</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>48069.0</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>72517.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>808044.0</v>
+      </c>
+      <c r="B202" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C202" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>11542.0</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>4205.0</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>7337.0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>808045.0</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C203" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>36815.0</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>17688.0</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>19127.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>808046.0</v>
+      </c>
+      <c r="B204" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C204" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>31065.0</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>7831.0</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>23234.0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>808047.0</v>
+      </c>
+      <c r="B205" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C205" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>46990.0</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>14260.0</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>32730.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>808048.0</v>
+      </c>
+      <c r="B206" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C206" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>32280.0</v>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>12759.0</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>19521.0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>808049.0</v>
+      </c>
+      <c r="B207" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C207" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>14413.0</v>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>3707.0</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>10706.0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>808050.0</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C208" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>18323.0</v>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>7554.0</v>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>10769.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>808080.0</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C209" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>4215.0</v>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>825.0</v>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>3390.0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>808084.0</v>
+      </c>
+      <c r="B210" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C210" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D210" s="1" t="n">
+        <v>3647.0</v>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>839.0</v>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>2808.0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>808101.0</v>
+      </c>
+      <c r="B211" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C211" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D211" s="1" t="n">
+        <v>345.0</v>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>245.0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>808102.0</v>
+      </c>
+      <c r="B212" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C212" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D212" s="1" t="n">
+        <v>8271.0</v>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>3993.0</v>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>4278.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>808103.0</v>
+      </c>
+      <c r="B213" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C213" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D213" s="1" t="n">
+        <v>8260.0</v>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>4681.0</v>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>3579.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>808104.0</v>
+      </c>
+      <c r="B214" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C214" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>385.0</v>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>334.0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>808111.0</v>
+      </c>
+      <c r="B215" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C215" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>1111.0</v>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>527.0</v>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>584.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>808113.0</v>
+      </c>
+      <c r="B216" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C216" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>808115.0</v>
+      </c>
+      <c r="B217" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C217" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>445.0</v>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>220.0</v>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>225.0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>808116.0</v>
+      </c>
+      <c r="B218" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C218" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>6945.0</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>2093.0</v>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>4852.0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>808117.0</v>
+      </c>
+      <c r="B219" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C219" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D219" s="1" t="n">
+        <v>232.0</v>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>173.0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>808121.0</v>
+      </c>
+      <c r="B220" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C220" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>577.0</v>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>487.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>808122.0</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C221" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>468.0</v>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>386.0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>808123.0</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C222" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>1065.0</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>142.0</v>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>923.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>808127.0</v>
+      </c>
+      <c r="B223" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C223" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>1333.0</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>329.0</v>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>1004.0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>808128.0</v>
+      </c>
+      <c r="B224" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C224" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>346.0</v>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>282.0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>808129.0</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C225" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>657.0</v>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>552.0</v>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>808131.0</v>
+      </c>
+      <c r="B226" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C226" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D226" s="1" t="n">
+        <v>4250.0</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>1822.0</v>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>2428.0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>808132.0</v>
+      </c>
+      <c r="B227" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>1526.0</v>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>459.0</v>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>1067.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>808133.0</v>
+      </c>
+      <c r="B228" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C228" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>613.0</v>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>485.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>808135.0</v>
+      </c>
+      <c r="B229" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C229" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>349.0</v>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>134.0</v>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>215.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>808136.0</v>
+      </c>
+      <c r="B230" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>431.0</v>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>345.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>808140.0</v>
+      </c>
+      <c r="B231" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C231" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>1126.0</v>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>670.0</v>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>456.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>808141.0</v>
+      </c>
+      <c r="B232" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D232" s="1" t="n">
+        <v>1073.0</v>
+      </c>
+      <c r="E232" s="2" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>918.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>808142.0</v>
+      </c>
+      <c r="B233" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D233" s="1" t="n">
+        <v>1707.0</v>
+      </c>
+      <c r="E233" s="2" t="n">
+        <v>389.0</v>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>1318.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>808143.0</v>
+      </c>
+      <c r="B234" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C234" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>4834.0</v>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>1789.0</v>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>3045.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>808144.0</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D235" s="1" t="n">
+        <v>556.0</v>
+      </c>
+      <c r="E235" s="2" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>439.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>808145.0</v>
+      </c>
+      <c r="B236" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D236" s="1" t="n">
+        <v>248.0</v>
+      </c>
+      <c r="E236" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>247.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>808146.0</v>
+      </c>
+      <c r="B237" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D237" s="1" t="n">
+        <v>220.0</v>
+      </c>
+      <c r="E237" s="2" t="n">
+        <v>201.0</v>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>808147.0</v>
+      </c>
+      <c r="B238" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="E238" s="2" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>28.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>808150.0</v>
+      </c>
+      <c r="B239" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D239" s="1" t="n">
+        <v>194.0</v>
+      </c>
+      <c r="E239" s="2" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>808151.0</v>
+      </c>
+      <c r="B240" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>1057.0</v>
+      </c>
+      <c r="E240" s="2" t="n">
+        <v>373.0</v>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>684.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>808181.0</v>
+      </c>
+      <c r="B241" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>776.0</v>
+      </c>
+      <c r="E241" s="2" t="n">
+        <v>395.0</v>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>381.0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>808182.0</v>
+      </c>
+      <c r="B242" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D242" s="1" t="n">
+        <v>48688.0</v>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>21578.0</v>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>27110.0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>808185.0</v>
+      </c>
+      <c r="B243" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>25082.0</v>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>11021.0</v>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>14061.0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>808209.0</v>
+      </c>
+      <c r="B244" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D244" s="1" t="n">
+        <v>14046.0</v>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>5813.0</v>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>8233.0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>808210.0</v>
+      </c>
+      <c r="B245" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D245" s="1" t="n">
+        <v>827.0</v>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>671.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>808301.0</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D246" s="1" t="n">
+        <v>9531.0</v>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>2442.0</v>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>7089.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>808305.0</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D247" s="1" t="n">
+        <v>4038.0</v>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>1077.0</v>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>2961.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>808312.0</v>
+      </c>
+      <c r="B248" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D248" s="1" t="n">
+        <v>1213.0</v>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>205.0</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>1008.0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>808313.0</v>
+      </c>
+      <c r="B249" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D249" s="1" t="n">
+        <v>322.0</v>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>279.0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>808320.0</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C250" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D250" s="1" t="n">
+        <v>166.0</v>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>136.0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>808321.0</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C251" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D251" s="1" t="n">
+        <v>336.0</v>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>103.0</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>233.0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>808322.0</v>
+      </c>
+      <c r="B252" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C252" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D252" s="1" t="n">
+        <v>2123.0</v>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>636.0</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>1487.0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>808323.0</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C253" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D253" s="1" t="n">
+        <v>18113.0</v>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>3888.0</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>14225.0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>808324.0</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C254" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D254" s="1" t="n">
+        <v>3777.0</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>1375.0</v>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>2402.0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>808325.0</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C255" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D255" s="1" t="n">
+        <v>3947.0</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>1082.0</v>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>2865.0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>808459.0</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C256" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D256" s="1" t="n">
+        <v>17720.0</v>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>8537.0</v>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>9183.0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>808460.0</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C257" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>341.0</v>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>252.0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>808461.0</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C258" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>1626.0</v>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>611.0</v>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>1015.0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>808462.0</v>
+      </c>
+      <c r="B259" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C259" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D259" s="1" t="n">
+        <v>338.0</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>279.0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>808463.0</v>
+      </c>
+      <c r="B260" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C260" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>430.0</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>320.0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>808501.0</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C261" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D261" s="1" t="n">
+        <v>2589.0</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>617.0</v>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>1972.0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>808502.0</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C262" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D262" s="1" t="n">
+        <v>1135.0</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>358.0</v>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>777.0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>808504.0</v>
+      </c>
+      <c r="B263" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C263" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D263" s="1" t="n">
+        <v>128.0</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>116.0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>808506.0</v>
+      </c>
+      <c r="B264" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C264" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D264" s="1" t="n">
+        <v>12676.0</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>2871.0</v>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>9805.0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>808507.0</v>
+      </c>
+      <c r="B265" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C265" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D265" s="1" t="n">
+        <v>287.0</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>261.0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>808508.0</v>
+      </c>
+      <c r="B266" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C266" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D266" s="1" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>76.0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>808601.0</v>
+      </c>
+      <c r="B267" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C267" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D267" s="1" t="n">
+        <v>7903.0</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>4402.0</v>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>3501.0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>808602.0</v>
+      </c>
+      <c r="B268" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C268" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>1102.0</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>334.0</v>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>768.0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>808603.0</v>
+      </c>
+      <c r="B269" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C269" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>2900.0</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>1090.0</v>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>1810.0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>808605.0</v>
+      </c>
+      <c r="B270" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C270" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>94.0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>808606.0</v>
+      </c>
+      <c r="B271" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C271" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D271" s="1" t="n">
+        <v>675.0</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>158.0</v>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>517.0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>808607.0</v>
+      </c>
+      <c r="B272" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C272" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D272" s="1" t="n">
+        <v>10879.0</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>3894.0</v>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>6985.0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>808609.0</v>
+      </c>
+      <c r="B273" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C273" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D273" s="1" t="n">
+        <v>15100.0</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>3855.0</v>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>11245.0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>808610.0</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C274" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D274" s="1" t="n">
+        <v>220.0</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>189.0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>808701.0</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C275" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D275" s="1" t="n">
+        <v>3510.0</v>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>1232.0</v>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>2278.0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>808702.0</v>
+      </c>
+      <c r="B276" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C276" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>291.0</v>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>129.0</v>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>162.0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>808801.0</v>
+      </c>
+      <c r="B277" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C277" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>447.0</v>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>385.0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>808802.0</v>
+      </c>
+      <c r="B278" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C278" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>199.0</v>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>159.0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>808803.0</v>
+      </c>
+      <c r="B279" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C279" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>927.0</v>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>819.0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>808804.0</v>
+      </c>
+      <c r="B280" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C280" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>396.0</v>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>368.0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>808805.0</v>
+      </c>
+      <c r="B281" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C281" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>573.0</v>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>229.0</v>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>344.0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>808807.0</v>
+      </c>
+      <c r="B282" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C282" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>531.0</v>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>469.0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>808808.0</v>
+      </c>
+      <c r="B283" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>503.0</v>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>145.0</v>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>358.0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>808809.0</v>
+      </c>
+      <c r="B284" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>331.0</v>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>133.0</v>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>198.0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>808810.0</v>
+      </c>
+      <c r="B285" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C285" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>808811.0</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C286" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D286" s="1" t="n">
+        <v>354.0</v>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="F286" s="3" t="n">
+        <v>273.0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>808812.0</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C287" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>48.0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>808814.0</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C288" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>759.0</v>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>172.0</v>
+      </c>
+      <c r="F288" s="3" t="n">
+        <v>587.0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>808816.0</v>
+      </c>
+      <c r="B289" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C289" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>144.0</v>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>126.0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>808817.0</v>
+      </c>
+      <c r="B290" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C290" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>336.0</v>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>314.0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>808818.0</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C291" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>354.0</v>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="F291" s="3" t="n">
+        <v>323.0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>808819.0</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C292" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>620.0</v>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>155.0</v>
+      </c>
+      <c r="F292" s="3" t="n">
+        <v>465.0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>808822.0</v>
+      </c>
+      <c r="B293" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C293" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>255.0</v>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>114.0</v>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>141.0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>808877.0</v>
+      </c>
+      <c r="B294" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C294" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D294" s="1" t="n">
+        <v>926.0</v>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>244.0</v>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>682.0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>808881.0</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C295" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>4988.0</v>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>1911.0</v>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>3077.0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>808882.0</v>
+      </c>
+      <c r="B296" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C296" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>3693.0</v>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>700.0</v>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>2993.0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>808885.0</v>
+      </c>
+      <c r="B297" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C297" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>387.0</v>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>317.0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>808887.0</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C298" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>960.0</v>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>814.0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>808888.0</v>
+      </c>
+      <c r="B299" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C299" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>677.0</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>674.0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>808892.0</v>
+      </c>
+      <c r="B300" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C300" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>754.0</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>171.0</v>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>583.0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>808894.0</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C301" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>659.0</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="F301" s="3" t="n">
+        <v>548.0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>808896.0</v>
+      </c>
+      <c r="B302" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C302" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>668.0</v>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>203.0</v>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>465.0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>808898.0</v>
+      </c>
+      <c r="B303" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C303" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>141.0</v>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="F303" s="3" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>808899.0</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C304" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>509.0</v>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>322.0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>808901.0</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C305" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>2988.0</v>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>1478.0</v>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>1510.0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>808902.0</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C306" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>1220.0</v>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>308.0</v>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>912.0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
         <v>808903.0</v>
       </c>
-      <c r="B117" t="n">
-        <v>2026.0</v>
-      </c>
-      <c r="C117" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>676.0</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>531.0</v>
+      <c r="B307" t="n">
+        <v>2026.0</v>
+      </c>
+      <c r="C307" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>805.0</v>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>191.0</v>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>614.0</v>
       </c>
     </row>
   </sheetData>
